--- a/AAII_Financials/Quarterly/PPWLO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PPWLO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -800,19 +800,19 @@
         <v>1327000</v>
       </c>
       <c r="F8" s="3">
-        <v>1484000</v>
+        <v>1484100</v>
       </c>
       <c r="G8" s="3">
         <v>1433000</v>
       </c>
       <c r="H8" s="3">
-        <v>1635000</v>
+        <v>1635100</v>
       </c>
       <c r="I8" s="3">
         <v>1314000</v>
       </c>
       <c r="J8" s="3">
-        <v>1297000</v>
+        <v>1297100</v>
       </c>
       <c r="K8" s="3">
         <v>1265000</v>
@@ -984,19 +984,19 @@
         <v>462000</v>
       </c>
       <c r="F10" s="3">
-        <v>165000</v>
+        <v>165100</v>
       </c>
       <c r="G10" s="3">
         <v>665000</v>
       </c>
       <c r="H10" s="3">
-        <v>765000</v>
+        <v>765100</v>
       </c>
       <c r="I10" s="3">
         <v>488000</v>
       </c>
       <c r="J10" s="3">
-        <v>555000</v>
+        <v>555100</v>
       </c>
       <c r="K10" s="3">
         <v>554000</v>
@@ -1512,16 +1512,16 @@
         <v>1651000</v>
       </c>
       <c r="G17" s="3">
-        <v>1086000</v>
+        <v>1085900</v>
       </c>
       <c r="H17" s="3">
-        <v>1198000</v>
+        <v>1198100</v>
       </c>
       <c r="I17" s="3">
         <v>1156000</v>
       </c>
       <c r="J17" s="3">
-        <v>1081000</v>
+        <v>1081100</v>
       </c>
       <c r="K17" s="3">
         <v>1043000</v>
@@ -1601,10 +1601,10 @@
         <v>131000</v>
       </c>
       <c r="F18" s="3">
-        <v>-167000</v>
+        <v>-166900</v>
       </c>
       <c r="G18" s="3">
-        <v>347000</v>
+        <v>347100</v>
       </c>
       <c r="H18" s="3">
         <v>437000</v>
@@ -1727,7 +1727,7 @@
         <v>63000</v>
       </c>
       <c r="F20" s="3">
-        <v>48000</v>
+        <v>47900</v>
       </c>
       <c r="G20" s="3">
         <v>36000</v>
@@ -1822,7 +1822,7 @@
         <v>160000</v>
       </c>
       <c r="G21" s="3">
-        <v>667000</v>
+        <v>667100</v>
       </c>
       <c r="H21" s="3">
         <v>745000</v>
@@ -2006,7 +2006,7 @@
         <v>-230000</v>
       </c>
       <c r="G23" s="3">
-        <v>280000</v>
+        <v>280100</v>
       </c>
       <c r="H23" s="3">
         <v>372000</v>
@@ -2282,7 +2282,7 @@
         <v>-120000</v>
       </c>
       <c r="G26" s="3">
-        <v>299000</v>
+        <v>299100</v>
       </c>
       <c r="H26" s="3">
         <v>409000</v>
@@ -2831,7 +2831,7 @@
         <v>-63000</v>
       </c>
       <c r="F32" s="3">
-        <v>-48000</v>
+        <v>-47900</v>
       </c>
       <c r="G32" s="3">
         <v>-36000</v>

--- a/AAII_Financials/Quarterly/PPWLO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PPWLO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
   <si>
     <t>PPWLO</t>
   </si>
@@ -656,416 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1548000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1449000</v>
+      </c>
+      <c r="F8" s="3">
         <v>1676000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1327000</v>
       </c>
-      <c r="F8" s="3">
-        <v>1484100</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>1484000</v>
+      </c>
+      <c r="I8" s="3">
         <v>1433000</v>
       </c>
-      <c r="H8" s="3">
-        <v>1635100</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
+        <v>1635000</v>
+      </c>
+      <c r="K8" s="3">
         <v>1314000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1297100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1265000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1491000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1298000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1242000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1512000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1479000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1144000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1206000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1275000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1367000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1167000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1259000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1280000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1369000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1193000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>1184000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>1281000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>1430000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>1245000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>1281000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>1282000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>1434000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1039000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>919000</v>
+      </c>
+      <c r="F9" s="3">
         <v>1020000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>865000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1319000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>768000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>870000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>826000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>742000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>711000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>772000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>696000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>683000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>871000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>831000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>626000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>671000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>767000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>716000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>639000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>721000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>718000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>731000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>663000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>683000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>728000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>719000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>657000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>695000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>720000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>750000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>509000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>530000</v>
+      </c>
+      <c r="F10" s="3">
         <v>656000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>462000</v>
       </c>
-      <c r="F10" s="3">
-        <v>165100</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>165000</v>
+      </c>
+      <c r="I10" s="3">
         <v>665000</v>
       </c>
-      <c r="H10" s="3">
-        <v>765100</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
+        <v>765000</v>
+      </c>
+      <c r="K10" s="3">
         <v>488000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>555100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>554000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>719000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>602000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>559000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>641000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>648000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>518000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>535000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>508000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>651000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>528000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>538000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>562000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>638000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>530000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>501000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>553000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>711000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>588000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>586000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>562000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>684000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1123,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1217,14 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,19 +1315,25 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F14" s="3">
         <v>1263000</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -1308,11 +1347,11 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1374,100 +1413,112 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>292000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>283000</v>
+      </c>
+      <c r="F15" s="3">
         <v>285000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>279000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>279000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>284000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>277000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>279000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>280000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>277000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>272000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>275000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>264000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>513000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>234000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>210000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>252000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>268000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>272000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>209000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>205000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>377000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>203000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>197000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>202000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>198000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>200000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>202000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>196000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>194000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1548,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1383000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1267000</v>
+      </c>
+      <c r="F17" s="3">
         <v>2619000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1196000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1651000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1085900</v>
-      </c>
-      <c r="H17" s="3">
-        <v>1198100</v>
-      </c>
       <c r="I17" s="3">
+        <v>1086000</v>
+      </c>
+      <c r="J17" s="3">
+        <v>1198000</v>
+      </c>
+      <c r="K17" s="3">
         <v>1156000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1081100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1043000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1098000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1014000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1008000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1439000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1118000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>888000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>972000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1088000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1034000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>899000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>975000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1146000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>983000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>909000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>937000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>974000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>969000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>907000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>942000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>963000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>990000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>165000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>182000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-943000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>131000</v>
       </c>
-      <c r="F18" s="3">
-        <v>-166900</v>
-      </c>
-      <c r="G18" s="3">
-        <v>347100</v>
-      </c>
       <c r="H18" s="3">
+        <v>-167000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>347000</v>
+      </c>
+      <c r="J18" s="3">
         <v>437000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>158000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>216000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>222000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>393000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>284000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>234000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>73000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>361000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>256000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>234000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>187000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>333000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>268000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>284000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>134000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>386000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>284000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>247000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>307000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>461000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>338000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>339000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>319000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>444000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,468 +1780,500 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>74000</v>
+      </c>
+      <c r="F20" s="3">
         <v>67000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>63000</v>
       </c>
-      <c r="F20" s="3">
-        <v>47900</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>48000</v>
+      </c>
+      <c r="I20" s="3">
         <v>36000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>31000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>17000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>16000</v>
-      </c>
-      <c r="K20" s="3">
-        <v>21000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>15000</v>
       </c>
       <c r="M20" s="3">
         <v>21000</v>
       </c>
       <c r="N20" s="3">
+        <v>15000</v>
+      </c>
+      <c r="O20" s="3">
+        <v>21000</v>
+      </c>
+      <c r="P20" s="3">
         <v>25000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>28000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>36000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>34000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>20000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>35000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>32000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>32000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>26000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-2000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>23000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>19000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>18000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>7000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>19000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>11000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>16000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>12000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>568000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>539000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-591000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>473000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>160000</v>
       </c>
-      <c r="G21" s="3">
-        <v>667100</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>667000</v>
+      </c>
+      <c r="J21" s="3">
         <v>745000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>454000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>512000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>520000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>680000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>580000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>523000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>614000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>631000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>500000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>506000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>490000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>637000</v>
-      </c>
-      <c r="U21" s="3">
-        <v>509000</v>
-      </c>
-      <c r="V21" s="3">
-        <v>515000</v>
       </c>
       <c r="W21" s="3">
         <v>509000</v>
       </c>
       <c r="X21" s="3">
+        <v>515000</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>509000</v>
+      </c>
+      <c r="Z21" s="3">
         <v>612000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>981000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>512000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>680000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>551000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>551000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>525000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>647000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>164000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>126000</v>
+      </c>
+      <c r="F22" s="3">
         <v>121000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>118000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>111000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>103000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>96000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>101000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>100000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>102000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>104000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>99000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>101000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>95000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>93000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>98000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>92000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>92000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>90000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>94000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>89000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>91000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>91000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>92000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>92000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>97000</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>91000</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>91000</v>
       </c>
       <c r="AD22" s="3">
         <v>91000</v>
       </c>
       <c r="AE22" s="3">
-        <v>92000</v>
+        <v>91000</v>
       </c>
       <c r="AF22" s="3">
         <v>91000</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>92000</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>91000</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>130000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-997000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>76000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-230000</v>
       </c>
-      <c r="G23" s="3">
-        <v>280100</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
+        <v>280000</v>
+      </c>
+      <c r="J23" s="3">
         <v>372000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>74000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>132000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>141000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>304000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>206000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>158000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>6000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>304000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>192000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>162000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>130000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>275000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>206000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>221000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>41000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>318000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>211000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>173000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>217000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>389000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>258000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>264000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>239000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>363000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-68000</v>
+      </c>
+      <c r="F24" s="3">
         <v>-345000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-30000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-110000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-19000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-37000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-8000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>2000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-21000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-28000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-19000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-11000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-105000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>18000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>26000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-14000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-16000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-3000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>38000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>42000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-95000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>48000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>27000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>25000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>66000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>126000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>83000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>85000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>70000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>110000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2364,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>121000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>198000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-652000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>106000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-120000</v>
       </c>
-      <c r="G26" s="3">
-        <v>299100</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>299000</v>
+      </c>
+      <c r="J26" s="3">
         <v>409000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>82000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>130000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>162000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>332000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>225000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>169000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>111000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>286000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>166000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>176000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>146000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>278000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>168000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>179000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>136000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>270000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>184000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>148000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>151000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>263000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>175000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>179000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>169000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>253000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>121000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>198000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-652000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>106000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-120000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>299000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>409000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>82000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>130000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>162000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>332000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>225000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>169000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>111000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>286000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>166000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>176000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>146000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>278000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>168000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>179000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>136000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>270000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>184000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>148000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>151000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>263000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>175000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>179000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>169000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>253000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2952,210 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-111000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-67000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-63000</v>
       </c>
-      <c r="F32" s="3">
-        <v>-47900</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-36000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-31000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-17000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-16000</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-21000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-15000</v>
       </c>
       <c r="M32" s="3">
         <v>-21000</v>
       </c>
       <c r="N32" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="P32" s="3">
         <v>-25000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-28000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-36000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-34000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-20000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-35000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-32000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-32000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-26000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>2000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-23000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-18000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-19000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-16000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-12000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-10000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>121000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>198000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-652000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>106000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-120000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>299000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>409000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>82000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>130000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>162000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>332000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>225000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>169000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>111000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>286000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>166000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>176000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>146000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>278000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>168000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>179000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>136000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>270000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>184000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>148000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>151000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>263000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>175000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>179000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>169000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>253000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3246,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>121000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>198000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-652000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>106000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-120000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>299000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>409000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>82000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>130000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>162000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>332000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>225000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>169000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>111000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>286000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>166000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>176000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>146000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>278000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>168000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>179000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>136000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>270000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>184000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>148000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>151000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>263000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>175000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>179000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>169000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>253000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3523,108 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2210000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>138000</v>
+      </c>
+      <c r="F41" s="3">
         <v>98000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>586000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>19000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>641000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>219000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>390000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>335000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>179000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>893000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>44000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>43000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>13000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>590000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>711000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>53000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>30000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>331000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>536000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>669000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>77000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>308000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>22000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>17000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>14000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>104000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>167000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>15000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>17000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>198000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,376 +3715,406 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>964000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1300000</v>
+      </c>
+      <c r="F43" s="3">
         <v>975000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>799000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>892000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>897000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>884000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>779000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>723000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>777000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>773000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>776000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>698000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>751000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>768000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>652000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>615000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>714000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>714000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>682000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>705000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>732000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>761000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>701000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>647000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>743000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>722000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>681000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>633000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>745000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>702000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>617000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>532000</v>
+      </c>
+      <c r="F44" s="3">
         <v>519000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>533000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>491000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>474000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>471000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>490000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>479000</v>
-      </c>
-      <c r="K44" s="3">
-        <v>474000</v>
-      </c>
-      <c r="L44" s="3">
-        <v>465000</v>
       </c>
       <c r="M44" s="3">
         <v>474000</v>
       </c>
       <c r="N44" s="3">
+        <v>465000</v>
+      </c>
+      <c r="O44" s="3">
+        <v>474000</v>
+      </c>
+      <c r="P44" s="3">
         <v>475000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>482000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>491000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>474000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>420000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>394000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>421000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>440000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>406000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>417000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>429000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>449000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>445000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>433000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>444000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>455000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>441000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>443000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>454000</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1093000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1017000</v>
+      </c>
+      <c r="F45" s="3">
         <v>722000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>537000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>631000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>672000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>408000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>360000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>433000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>291000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>336000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>269000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>289000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>277000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>233000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>170000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>157000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>152000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>137000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>139000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>152000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>133000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>114000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>140000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>128000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>215000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>102000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>103000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>113000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>149000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>121000</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4884000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2987000</v>
+      </c>
+      <c r="F46" s="3">
         <v>2314000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2455000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2033000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>2684000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1982000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2019000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1970000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1721000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>2467000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1563000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1505000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1523000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>2082000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2007000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1245000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1290000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1603000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1797000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1932000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1359000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>1612000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1312000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>1237000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1315000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>1372000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>1406000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>1202000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>1354000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>1475000</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3996,100 +4205,112 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>27471000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>27061000</v>
+      </c>
+      <c r="F48" s="3">
         <v>26099000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>25488000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>24695000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>24439000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>23893000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>23414000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>23081000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>22914000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>22748000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>22675000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>22535000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>22430000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>22042000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>21553000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>21099000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>20992000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>20627000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>20176000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>19718000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>19591000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>19338000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>19292000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>19190000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>19203000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>19135000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>19141000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>19130000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>19162000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>19047000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4401,14 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4597,112 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2530000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2562000</v>
+      </c>
+      <c r="F52" s="3">
         <v>2954000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>2609000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>2391000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>2282000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>2138000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>2007000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1793000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1821000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1856000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1845000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1758000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1749000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1403000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>1407000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1448000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1415000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1396000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>1393000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1399000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>1363000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1386000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>1355000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>1398000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>1402000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>1906000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>1913000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>1905000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>1878000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>1867000</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4793,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>34885000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>32610000</v>
+      </c>
+      <c r="F54" s="3">
         <v>31367000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>30552000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>29119000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>29405000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>28013000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>27440000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>26844000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>26456000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>27071000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>26083000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>25798000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>25702000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>25527000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>24967000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>23792000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>23697000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>23626000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>23366000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>23049000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>22313000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>22336000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>21959000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>21825000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>21920000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>22413000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>22460000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>22237000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>22394000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>22389000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,560 +4967,598 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1361000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1560000</v>
+      </c>
+      <c r="F57" s="3">
         <v>1204000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1036000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>900000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1049000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1103000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>848000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>724000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>680000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>624000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>667000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>615000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>772000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>764000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>685000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>660000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>679000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>732000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>670000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>583000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>597000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>438000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>390000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>376000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>453000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>398000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>397000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>371000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>408000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>410000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>591000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2195000</v>
+      </c>
+      <c r="F58" s="3">
         <v>638000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>565000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>440000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>449000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>452000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>455000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>155000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>155000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>574000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>780000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>974000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>513000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>438000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>438000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>94000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>168000</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
       <c r="V58" s="3">
         <v>0</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
         <v>382000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>352000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>960000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>975000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>668000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>591000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>92000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>101000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>328000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>67000</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1311000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>821000</v>
+      </c>
+      <c r="F59" s="3">
         <v>915000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>841000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>818000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>648000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>827000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>738000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>647000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>625000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>744000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>712000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>633000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>580000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>653000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>621000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>609000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>513000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>641000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>698000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>634000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>536000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>696000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>632000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>582000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>496000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>652000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>690000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>566000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>463000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>678000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3263000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4576000</v>
+      </c>
+      <c r="F60" s="3">
         <v>2757000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2442000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2158000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2146000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2382000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2041000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1526000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1460000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1942000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2159000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2222000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1865000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1855000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1744000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1363000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1360000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1373000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1368000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1217000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1515000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1486000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1982000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>1933000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>1617000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>1641000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>1179000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>1038000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>1199000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>1155000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>13584000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>9819000</v>
+      </c>
+      <c r="F61" s="3">
         <v>9984000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>9984000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>9218000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>9217000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>8177000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>8268000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>8567000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>8575000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>8625000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>7735000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>7734000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>8192000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>8211000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>8210000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>7621000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>7620000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>7657000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>7656000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>7656000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>6684000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>6682000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>6088000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>6087000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>6437000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>6436000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>6935000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>6934000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>7021000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>7026000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7945000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>8243000</v>
+      </c>
+      <c r="F62" s="3">
         <v>8851000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>7699000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>7422000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>7301000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>7019000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>7105000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>6707000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>6508000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>6604000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>6622000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>6500000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>6472000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>6395000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>6233000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>6194000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>6280000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>6301000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>6325000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>6326000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>6269000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>6411000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>6352000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>6352000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>6311000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>6829000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>6802000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>6796000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>6784000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>6661000</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5845,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24792000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>22638000</v>
+      </c>
+      <c r="F66" s="3">
         <v>21592000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>20125000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>18798000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>18664000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>17578000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>17414000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>16800000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>16543000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>17171000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>16516000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>16456000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>16529000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>16461000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>16187000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>15178000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>15260000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>15331000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>15349000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>15199000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>14468000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>14579000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>14422000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>14372000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>14365000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>14906000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>14916000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>14768000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>15004000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>14842000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>2000</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5622000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>5501000</v>
+      </c>
+      <c r="F72" s="3">
         <v>5303000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>5955000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>5849000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>6269000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>5970000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>5561000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>5579000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>5449000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>5437000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>5105000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>4880000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>4711000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>4600000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>4314000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>4148000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>3972000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>3826000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>3548000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>3381000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>3377000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>3291000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>3071000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>2987000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>3089000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>3038000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>3075000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>3000000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>2921000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>3077000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10091000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>9970000</v>
+      </c>
+      <c r="F76" s="3">
         <v>9773000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>10425000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>10319000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>10739000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>10433000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>10024000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>10042000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>9911000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>9898000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>9565000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>9340000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>9171000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>9064000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>8778000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>8612000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>8435000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>8293000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>8015000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>7848000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>7843000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>7755000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>7535000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>7451000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>7553000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>7505000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>7542000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>7467000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>7388000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>7545000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6959,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>121000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>198000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-652000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>106000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-120000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>299000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>409000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>82000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>130000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>162000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>332000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>225000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>169000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>111000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>286000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>166000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>176000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>146000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>278000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>168000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>179000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>136000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>270000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>184000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>148000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>151000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>263000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>175000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>179000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>169000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>253000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7200,108 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>292000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>283000</v>
+      </c>
+      <c r="F83" s="3">
         <v>285000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>279000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>279000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>284000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>277000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>279000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>280000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>277000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>272000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>275000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>264000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>513000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>234000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>210000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>252000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>268000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>272000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>209000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>205000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>377000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>203000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>-317000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>716000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>198000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>200000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>202000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>196000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>194000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7784,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>683000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-367000</v>
+      </c>
+      <c r="F89" s="3">
         <v>160000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>568000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>339000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>67000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>539000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>676000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>537000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>260000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>498000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>577000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>469000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>292000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>521000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>333000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>437000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>280000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>425000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>348000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>494000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>331000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>563000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-562000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>1479000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>141000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>432000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>441000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>588000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>196000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>575000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7922,108 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-774000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-976000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-721000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-886000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-643000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-685000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-587000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-520000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-374000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-356000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-338000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-380000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-439000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-922000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-645000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-607000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-366000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-726000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-632000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-480000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-337000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-544000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-214000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-263000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-236000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-216000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-183000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-192000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-356000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-317000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-171000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +8212,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-768000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-976000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-716000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-885000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-644000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-684000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-589000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-517000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-371000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-351000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-331000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-379000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-440000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-923000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-643000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-605000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-339000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-724000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-627000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-477000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-336000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-541000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-212000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-262000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-237000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-208000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-166000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-197000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-158000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-309000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-136000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7897,14 +8364,14 @@
         <v>0</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>-300000</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
@@ -7945,40 +8412,46 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-175000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-50000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-50000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-100000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-250000</v>
       </c>
       <c r="AA96" s="3">
         <v>-100000</v>
       </c>
       <c r="AB96" s="3">
-        <v>-300000</v>
+        <v>-250000</v>
       </c>
       <c r="AC96" s="3">
         <v>-100000</v>
       </c>
       <c r="AD96" s="3">
+        <v>-300000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-100000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-325000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-300000</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,100 +8738,112 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2159000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1390000</v>
+      </c>
+      <c r="F100" s="3">
         <v>72000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>888000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-311000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>1036000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-95000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-100000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-11000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-622000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>682000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-197000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>1000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>53000</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>931000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-74000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>128000</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>-1000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>434000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-21000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-65000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-746000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>336000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-22000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-303000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-111000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-413000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-68000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-300000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8413,18 +8910,18 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-      <c r="Y101" s="3" t="s">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>1000</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
         <v>0</v>
       </c>
@@ -8437,96 +8934,108 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2074000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>47000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-484000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>571000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-616000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>419000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-145000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>59000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>155000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-713000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>849000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>1000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>30000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-578000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-122000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>659000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>24000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-316000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-202000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-130000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>592000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-231000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>286000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-585000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>593000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-90000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-63000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>152000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-181000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>139000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PPWLO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PPWLO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>PPWLO</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1489000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1548000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1449000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1676000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1327000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1484000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1433000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1635000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1314000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1297100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1265000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1491000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1298000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1242000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1512000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1479000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1144000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1206000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1275000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1367000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1167000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1259000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1280000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1369000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1193000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1184000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1281000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1430000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1245000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1281000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1282000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1434000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1001000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1039000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>919000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1020000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>865000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1319000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>768000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>870000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>826000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>742000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>711000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>772000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>696000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>683000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>871000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>831000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>626000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>671000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>767000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>716000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>639000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>721000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>718000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>731000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>663000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>683000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>728000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>719000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>657000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>695000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>720000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>750000</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>488000</v>
+      </c>
+      <c r="E10" s="3">
         <v>509000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>530000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>656000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>462000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>165000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>665000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>765000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>488000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>555100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>554000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>719000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>602000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>559000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>641000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>648000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>518000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>535000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>508000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>651000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>528000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>538000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>562000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>638000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>530000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>501000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>553000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>711000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>588000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>586000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>562000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>684000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,22 +1338,25 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>251000</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>6000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1263000</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -1353,8 +1373,8 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1419,106 +1439,112 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>287000</v>
+      </c>
+      <c r="E15" s="3">
         <v>292000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>283000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>285000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>279000</v>
       </c>
       <c r="H15" s="3">
         <v>279000</v>
       </c>
       <c r="I15" s="3">
+        <v>279000</v>
+      </c>
+      <c r="J15" s="3">
         <v>284000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>277000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>279000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>280000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>277000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>272000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>275000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>264000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>513000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>234000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>210000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>252000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>268000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>272000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>209000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>205000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>377000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>203000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>197000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>202000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>198000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>200000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>202000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>196000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>194000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1593000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1383000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1267000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2619000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1196000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1651000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1086000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1198000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1156000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1081100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1043000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1098000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1014000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1008000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1439000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1118000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>888000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>972000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1088000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1034000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>899000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>975000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1146000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>983000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>909000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>937000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>974000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>969000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>907000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>942000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>963000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>990000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-104000</v>
+      </c>
+      <c r="E18" s="3">
         <v>165000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>182000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-943000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>131000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-167000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>347000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>437000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>158000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>216000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>222000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>393000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>284000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>234000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>73000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>361000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>256000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>234000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>187000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>333000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>268000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>284000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>134000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>386000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>284000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>247000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>307000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>461000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>338000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>339000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>319000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>444000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,287 +1815,294 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>104000</v>
+      </c>
+      <c r="E20" s="3">
         <v>111000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>74000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>67000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>63000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>48000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>36000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>31000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>17000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>16000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>21000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>15000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>21000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>25000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>28000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>36000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>34000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>20000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>35000</v>
-      </c>
-      <c r="V20" s="3">
-        <v>32000</v>
       </c>
       <c r="W20" s="3">
         <v>32000</v>
       </c>
       <c r="X20" s="3">
+        <v>32000</v>
+      </c>
+      <c r="Y20" s="3">
         <v>26000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>23000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>19000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>18000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>7000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>19000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>11000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>16000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>12000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>287000</v>
+      </c>
+      <c r="E21" s="3">
         <v>568000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>539000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-591000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>473000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>160000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>667000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>745000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>454000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>512000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>520000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>680000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>580000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>523000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>614000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>631000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>500000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>506000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>490000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>637000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>509000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>515000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>509000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>612000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-14000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>981000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>512000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>680000</v>
-      </c>
-      <c r="AE21" s="3">
-        <v>551000</v>
       </c>
       <c r="AF21" s="3">
         <v>551000</v>
       </c>
       <c r="AG21" s="3">
+        <v>551000</v>
+      </c>
+      <c r="AH21" s="3">
         <v>525000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>647000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>154000</v>
+      </c>
+      <c r="E22" s="3">
         <v>164000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>126000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>121000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>118000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>111000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>103000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>96000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>101000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>100000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>102000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>104000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>99000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>101000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>95000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>93000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>98000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>92000</v>
       </c>
       <c r="U22" s="3">
         <v>92000</v>
       </c>
       <c r="V22" s="3">
+        <v>92000</v>
+      </c>
+      <c r="W22" s="3">
         <v>90000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>94000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>89000</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>91000</v>
       </c>
       <c r="Z22" s="3">
         <v>91000</v>
       </c>
       <c r="AA22" s="3">
-        <v>92000</v>
+        <v>91000</v>
       </c>
       <c r="AB22" s="3">
         <v>92000</v>
       </c>
       <c r="AC22" s="3">
+        <v>92000</v>
+      </c>
+      <c r="AD22" s="3">
         <v>97000</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>91000</v>
       </c>
       <c r="AE22" s="3">
         <v>91000</v>
@@ -2071,209 +2111,218 @@
         <v>91000</v>
       </c>
       <c r="AG22" s="3">
+        <v>91000</v>
+      </c>
+      <c r="AH22" s="3">
         <v>92000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>91000</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-154000</v>
+      </c>
+      <c r="E23" s="3">
         <v>112000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>130000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-997000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>76000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-230000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>280000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>372000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>74000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>132000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>141000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>304000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>206000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>158000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>304000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>192000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>162000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>130000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>275000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>206000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>221000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>41000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>318000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>211000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>173000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>217000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>389000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>258000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>264000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>239000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>363000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-85000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-9000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-68000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-345000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-30000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-110000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-19000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-37000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-8000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-21000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-28000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-19000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-105000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>18000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>26000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-14000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-16000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-3000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>38000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>42000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-95000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>48000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>27000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>25000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>66000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>126000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>83000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>85000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>70000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>110000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-69000</v>
+      </c>
+      <c r="E26" s="3">
         <v>121000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>198000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-652000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>106000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-120000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>299000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>409000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>82000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>130000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>162000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>332000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>225000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>169000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>111000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>286000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>166000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>176000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>146000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>278000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>168000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>179000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>136000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>270000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>184000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>148000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>151000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>263000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>175000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>179000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>169000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>253000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-69000</v>
+      </c>
+      <c r="E27" s="3">
         <v>121000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>198000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-652000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>106000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-120000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>299000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>409000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>82000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>130000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>162000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>332000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>225000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>169000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>111000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>286000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>166000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>176000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>146000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>278000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>168000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>179000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>136000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>270000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>184000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>148000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>151000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>263000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>175000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>179000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>169000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>253000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-104000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-111000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-74000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-67000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-63000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-48000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-36000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-31000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-17000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-16000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-21000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-15000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-21000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-25000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-28000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-36000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-34000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-20000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-35000</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-32000</v>
       </c>
       <c r="W32" s="3">
         <v>-32000</v>
       </c>
       <c r="X32" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-26000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-23000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-19000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-18000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-19000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-16000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-12000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-10000</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-69000</v>
+      </c>
+      <c r="E33" s="3">
         <v>121000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>198000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-652000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>106000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-120000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>299000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>409000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>82000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>130000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>162000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>332000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>225000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>169000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>111000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>286000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>166000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>176000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>146000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>278000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>168000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>179000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>136000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>270000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>184000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>148000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>151000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>263000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>175000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>179000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>169000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>253000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-69000</v>
+      </c>
+      <c r="E35" s="3">
         <v>121000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>198000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-652000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>106000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-120000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>299000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>409000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>82000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>130000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>162000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>332000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>225000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>169000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>111000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>286000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>166000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>176000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>146000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>278000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>168000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>179000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>136000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>270000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>184000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>148000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>151000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>263000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>175000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>179000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>169000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>253000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1289000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2210000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>138000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>98000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>586000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>19000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>641000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>219000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>390000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>335000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>179000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>893000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>44000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>43000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>13000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>590000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>711000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>53000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>30000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>331000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>536000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>669000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>77000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>308000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>22000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>17000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>14000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>104000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>167000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>15000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>17000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>198000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,400 +3811,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1039000</v>
+      </c>
+      <c r="E43" s="3">
         <v>964000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1300000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>975000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>799000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>892000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>897000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>884000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>779000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>723000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>777000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>773000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>776000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>698000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>751000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>768000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>652000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>615000</v>
-      </c>
-      <c r="U43" s="3">
-        <v>714000</v>
       </c>
       <c r="V43" s="3">
         <v>714000</v>
       </c>
       <c r="W43" s="3">
+        <v>714000</v>
+      </c>
+      <c r="X43" s="3">
         <v>682000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>705000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>732000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>761000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>701000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>647000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>743000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>722000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>681000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>633000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>745000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>702000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>690000</v>
+      </c>
+      <c r="E44" s="3">
         <v>617000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>532000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>519000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>533000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>491000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>474000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>471000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>490000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>479000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>474000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>465000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>474000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>475000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>482000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>491000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>474000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>420000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>394000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>421000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>440000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>406000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>417000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>429000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>449000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>445000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>433000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>444000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>455000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>441000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>443000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>454000</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1120000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1093000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1017000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>722000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>537000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>631000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>672000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>408000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>360000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>433000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>291000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>336000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>269000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>289000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>277000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>233000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>170000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>157000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>152000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>137000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>139000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>152000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>133000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>114000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>140000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>128000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>215000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>102000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>103000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>113000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>149000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>121000</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4138000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4884000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2987000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2314000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2455000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2033000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2684000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1982000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2019000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1970000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1721000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2467000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1563000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1505000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1523000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2082000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2007000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1245000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1290000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1603000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1797000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1932000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1359000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1612000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1312000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1237000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1315000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1372000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1406000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1202000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1354000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1475000</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4211,106 +4316,112 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>27941000</v>
+      </c>
+      <c r="E48" s="3">
         <v>27471000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>27061000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>26099000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>25488000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>24695000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>24439000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>23893000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>23414000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>23081000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22914000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>22748000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>22675000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>22535000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>22430000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>22042000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21553000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21099000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20992000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20627000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20176000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>19718000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19591000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>19338000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>19292000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>19190000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>19203000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>19135000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>19141000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>19130000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>19162000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>19047000</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2529000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2530000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2562000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2954000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2609000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2391000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2282000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2138000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2007000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1793000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1821000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1856000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1845000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1758000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1749000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1403000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1407000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1448000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1415000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1396000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1393000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1399000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1363000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1386000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1355000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1398000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1402000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1906000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1913000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1905000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1878000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1867000</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>34608000</v>
+      </c>
+      <c r="E54" s="3">
         <v>34885000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>32610000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>31367000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>30552000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>29119000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>29405000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>28013000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27440000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>26844000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>26456000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>27071000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>26083000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>25798000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>25702000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>25527000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>24967000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>23792000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>23697000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>23626000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>23366000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>23049000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>22313000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>22336000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>21959000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>21825000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>21920000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>22413000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>22460000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>22237000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>22394000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>22389000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,166 +5099,170 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1396000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1361000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1560000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1204000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1036000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>900000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1049000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1103000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>848000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>724000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>680000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>624000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>667000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>615000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>772000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>764000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>685000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>660000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>679000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>732000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>670000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>583000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>597000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>438000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>390000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>376000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>453000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>398000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>397000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>371000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>408000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>410000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>166000</v>
+      </c>
+      <c r="E58" s="3">
         <v>591000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2195000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>638000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>565000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>440000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>449000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>452000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>455000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>155000</v>
       </c>
       <c r="M58" s="3">
         <v>155000</v>
       </c>
       <c r="N58" s="3">
+        <v>155000</v>
+      </c>
+      <c r="O58" s="3">
         <v>574000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>780000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>974000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>513000</v>
-      </c>
-      <c r="R58" s="3">
-        <v>438000</v>
       </c>
       <c r="S58" s="3">
         <v>438000</v>
       </c>
       <c r="T58" s="3">
+        <v>438000</v>
+      </c>
+      <c r="U58" s="3">
         <v>94000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>168000</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
       <c r="W58" s="3">
         <v>0</v>
       </c>
@@ -5136,233 +5270,242 @@
         <v>0</v>
       </c>
       <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>382000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>352000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>960000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>975000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>668000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>591000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>92000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>101000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>328000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>67000</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1502000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1311000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>821000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>915000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>841000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>818000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>648000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>827000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>738000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>647000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>625000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>744000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>712000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>633000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>580000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>653000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>621000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>609000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>513000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>641000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>698000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>634000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>536000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>696000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>632000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>582000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>496000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>652000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>690000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>566000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>463000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>678000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3064000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3263000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4576000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2757000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2442000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2158000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2146000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2382000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2041000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1526000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1460000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1942000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2159000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2222000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1865000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1855000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1744000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1363000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1360000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1373000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1368000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1217000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1515000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1486000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1982000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1933000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1617000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1641000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1179000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1038000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1199000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1155000</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5370,195 +5513,201 @@
         <v>13584000</v>
       </c>
       <c r="E61" s="3">
+        <v>13584000</v>
+      </c>
+      <c r="F61" s="3">
         <v>9819000</v>
-      </c>
-      <c r="F61" s="3">
-        <v>9984000</v>
       </c>
       <c r="G61" s="3">
         <v>9984000</v>
       </c>
       <c r="H61" s="3">
+        <v>9984000</v>
+      </c>
+      <c r="I61" s="3">
         <v>9218000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9217000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8177000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8268000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8567000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8575000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8625000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7735000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7734000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8192000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8211000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8210000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7621000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7620000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7657000</v>
-      </c>
-      <c r="W61" s="3">
-        <v>7656000</v>
       </c>
       <c r="X61" s="3">
         <v>7656000</v>
       </c>
       <c r="Y61" s="3">
+        <v>7656000</v>
+      </c>
+      <c r="Z61" s="3">
         <v>6684000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6682000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6088000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6087000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6437000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6436000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6935000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6934000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7021000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7026000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7936000</v>
+      </c>
+      <c r="E62" s="3">
         <v>7945000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8243000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8851000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7699000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7422000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7301000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7019000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7105000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6707000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6508000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6604000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6622000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6500000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6472000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6395000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6233000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6194000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>6280000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>6301000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>6325000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>6326000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>6269000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>6411000</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>6352000</v>
       </c>
       <c r="AB62" s="3">
         <v>6352000</v>
       </c>
       <c r="AC62" s="3">
+        <v>6352000</v>
+      </c>
+      <c r="AD62" s="3">
         <v>6311000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>6829000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>6802000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>6796000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>6784000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>6661000</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24584000</v>
+      </c>
+      <c r="E66" s="3">
         <v>24792000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>22638000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>21592000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>20125000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>18798000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>18664000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>17578000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>17414000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16800000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16543000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>17171000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16516000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>16456000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>16529000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>16461000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>16187000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>15178000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>15260000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>15331000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>15349000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>15199000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>14468000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>14579000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>14422000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>14372000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>14365000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>14906000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>14916000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>14768000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>15004000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>14842000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>2000</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5553000</v>
+      </c>
+      <c r="E72" s="3">
         <v>5622000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5501000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5303000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5955000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5849000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6269000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5970000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5561000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5579000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5449000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5437000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5105000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4880000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>4711000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>4600000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>4314000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4148000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3972000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3826000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3548000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3381000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3377000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3291000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>3071000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2987000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>3089000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>3038000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>3075000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>3000000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2921000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>3077000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10022000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10091000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9970000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9773000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10425000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10319000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10739000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10433000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10024000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10042000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9911000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9898000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9565000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9340000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9171000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9064000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8778000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8612000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8435000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8293000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8015000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7848000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7843000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7755000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7535000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7451000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7553000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7505000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7542000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7467000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>7388000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>7545000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-69000</v>
+      </c>
+      <c r="E81" s="3">
         <v>121000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>198000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-652000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>106000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-120000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>299000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>409000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>82000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>130000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>162000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>332000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>225000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>169000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>111000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>286000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>166000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>176000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>146000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>278000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>168000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>179000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>136000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>270000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>184000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>148000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>151000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>263000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>175000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>179000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>169000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>253000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>287000</v>
+      </c>
+      <c r="E83" s="3">
         <v>292000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>283000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>285000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>279000</v>
       </c>
       <c r="H83" s="3">
         <v>279000</v>
       </c>
       <c r="I83" s="3">
+        <v>279000</v>
+      </c>
+      <c r="J83" s="3">
         <v>284000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>277000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>279000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>280000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>277000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>272000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>275000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>264000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>513000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>234000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>210000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>252000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>268000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>272000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>209000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>205000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>377000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>203000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>-317000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>716000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>198000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>200000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>202000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>196000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>194000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>193000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>214000</v>
+      </c>
+      <c r="E89" s="3">
         <v>683000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-367000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>160000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>568000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>339000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>67000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>539000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>676000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>537000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>260000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>498000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>577000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>469000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>292000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>521000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>333000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>437000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>280000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>425000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>348000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>494000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>331000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>563000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-562000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1479000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>141000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>432000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>441000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>588000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>196000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>575000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-704000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-774000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-976000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-721000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-886000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-643000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-685000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-587000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-520000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-374000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-356000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-338000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-380000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-439000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-922000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-645000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-607000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-366000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-726000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-632000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-480000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-337000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-544000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-214000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-263000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-236000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-216000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-183000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-192000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-356000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-317000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-171000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-703000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-768000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-976000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-716000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-885000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-644000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-684000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-589000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-517000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-371000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-351000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-331000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-379000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-440000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-923000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-643000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-605000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-339000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-724000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-627000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-477000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-336000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-541000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-212000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-262000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-237000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-208000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-166000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-197000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-158000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-309000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-136000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8370,11 +8604,11 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>-300000</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
@@ -8418,40 +8652,43 @@
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-175000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-50000</v>
       </c>
       <c r="Z96" s="3">
         <v>-50000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-50000</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-100000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-250000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-100000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-300000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-100000</v>
       </c>
       <c r="AF96" s="3">
         <v>-100000</v>
       </c>
       <c r="AG96" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-325000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-300000</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,106 +8987,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-428000</v>
+      </c>
+      <c r="E100" s="3">
         <v>2159000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1390000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>72000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>888000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-311000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1036000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-95000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-100000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-11000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-622000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>682000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-197000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>53000</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>931000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-74000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>128000</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>-1000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>434000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-21000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-65000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-746000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>336000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-22000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-303000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-111000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-413000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-68000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-300000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8916,15 +9165,15 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-      <c r="AA101" s="3" t="s">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1000</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
         <v>0</v>
       </c>
@@ -8940,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-917000</v>
+      </c>
+      <c r="E102" s="3">
         <v>2074000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>47000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-484000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>571000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-616000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>419000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-145000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>59000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>155000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-713000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>849000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>30000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-578000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-122000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>659000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>24000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-316000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-202000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-130000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>592000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-231000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>286000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-585000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>593000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-90000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-63000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>152000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-181000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>139000</v>
       </c>
     </row>
